--- a/VanHanhCD1/wwwroot/templates/BMVH_LoVoiQuay.xlsx
+++ b/VanHanhCD1/wwwroot/templates/BMVH_LoVoiQuay.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\03. Project Hoa Phat\07. Backend\VanHanhCD1_API-main\VanHanhCD1\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D111667-093D-4935-9F43-B8CB21F56DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81563F31-36B4-4B42-BFFB-69D0F56FBAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -699,6 +699,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -744,12 +745,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -771,7 +766,12 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -790,173 +790,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>30940</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>253303</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="4" name="Group 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49E52B96-7BA9-46E5-B913-38F5BAF64C25}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="0" y="60960"/>
-          <a:ext cx="2050240" cy="830518"/>
-          <a:chOff x="2095144" y="2853014"/>
-          <a:chExt cx="2106718" cy="826708"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="5" name="Picture 4">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{769C2D78-491B-4CBE-B0F9-9773543632CB}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-            <a:extLst>
-              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-              </a:ext>
-            </a:extLst>
-          </a:blip>
-          <a:srcRect/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="2200810" y="2853014"/>
-            <a:ext cx="1882509" cy="331302"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="6" name="TextBox 4">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC263439-9B1C-412A-AE23-10A0D1761892}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1">
-            <a:spLocks noChangeArrowheads="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="2095144" y="3187296"/>
-            <a:ext cx="2106718" cy="492426"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:txBody>
-          <a:bodyPr rot="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" anchor="ctr" anchorCtr="0" upright="1">
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr marL="0" marR="0" algn="ctr">
-              <a:lnSpc>
-                <a:spcPts val="1200"/>
-              </a:lnSpc>
-              <a:spcBef>
-                <a:spcPts val="0"/>
-              </a:spcBef>
-              <a:spcAft>
-                <a:spcPts val="800"/>
-              </a:spcAft>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:effectLst/>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-              <a:t>CÔNG TY CỔ PHẦN THÉP</a:t>
-            </a:r>
-            <a:br>
-              <a:rPr lang="en-US" sz="1200" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:effectLst/>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-            </a:br>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200" b="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:effectLst/>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-              <a:t>HÒA PHÁT DUNG QUẤT</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" sz="1100">
-              <a:effectLst/>
-              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1475,235 +1308,235 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="AD1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE1" s="24"/>
-      <c r="AF1" s="24"/>
-      <c r="AG1" s="24"/>
-      <c r="AH1" s="24"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="AD1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE1" s="25"/>
+      <c r="AF1" s="25"/>
+      <c r="AG1" s="25"/>
+      <c r="AH1" s="25"/>
     </row>
     <row r="2" spans="1:38" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L2" s="2"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
       <c r="AB2" s="9"/>
       <c r="AC2" s="9"/>
-      <c r="AD2" s="24" t="s">
+      <c r="AD2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="AE2" s="24"/>
-      <c r="AF2" s="24"/>
-      <c r="AG2" s="24"/>
-      <c r="AH2" s="24"/>
+      <c r="AE2" s="25"/>
+      <c r="AF2" s="25"/>
+      <c r="AG2" s="25"/>
+      <c r="AH2" s="25"/>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:38" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="26"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="26"/>
-      <c r="S4" s="26"/>
-      <c r="T4" s="26"/>
-      <c r="U4" s="26"/>
-      <c r="V4" s="26"/>
-      <c r="W4" s="26"/>
-      <c r="X4" s="26"/>
-      <c r="Y4" s="26"/>
-      <c r="Z4" s="26"/>
-      <c r="AA4" s="26"/>
-      <c r="AB4" s="26"/>
-      <c r="AC4" s="26"/>
-      <c r="AD4" s="26"/>
-      <c r="AE4" s="26"/>
-      <c r="AF4" s="26"/>
-      <c r="AG4" s="26"/>
-      <c r="AH4" s="26"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="27"/>
+      <c r="AC4" s="27"/>
+      <c r="AD4" s="27"/>
+      <c r="AE4" s="27"/>
+      <c r="AF4" s="27"/>
+      <c r="AG4" s="27"/>
+      <c r="AH4" s="27"/>
     </row>
     <row r="5" spans="1:38" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="22"/>
-      <c r="V5" s="22"/>
-      <c r="W5" s="22"/>
-      <c r="X5" s="22"/>
-      <c r="Y5" s="22"/>
-      <c r="Z5" s="22"/>
-      <c r="AA5" s="22"/>
-      <c r="AB5" s="22"/>
-      <c r="AC5" s="22"/>
-      <c r="AD5" s="22"/>
-      <c r="AE5" s="22"/>
-      <c r="AF5" s="22"/>
-      <c r="AG5" s="22"/>
-      <c r="AH5" s="22"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="23"/>
+      <c r="T5" s="23"/>
+      <c r="U5" s="23"/>
+      <c r="V5" s="23"/>
+      <c r="W5" s="23"/>
+      <c r="X5" s="23"/>
+      <c r="Y5" s="23"/>
+      <c r="Z5" s="23"/>
+      <c r="AA5" s="23"/>
+      <c r="AB5" s="23"/>
+      <c r="AC5" s="23"/>
+      <c r="AD5" s="23"/>
+      <c r="AE5" s="23"/>
+      <c r="AF5" s="23"/>
+      <c r="AG5" s="23"/>
+      <c r="AH5" s="23"/>
     </row>
     <row r="6" spans="1:38" s="3" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23" t="s">
+      <c r="A6" s="24"/>
+      <c r="B6" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23" t="s">
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23" t="s">
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="23"/>
-      <c r="T6" s="23"/>
-      <c r="U6" s="23" t="s">
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="24"/>
+      <c r="U6" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="V6" s="23"/>
-      <c r="W6" s="23"/>
-      <c r="X6" s="23"/>
-      <c r="Y6" s="23"/>
-      <c r="Z6" s="23" t="s">
+      <c r="V6" s="24"/>
+      <c r="W6" s="24"/>
+      <c r="X6" s="24"/>
+      <c r="Y6" s="24"/>
+      <c r="Z6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AA6" s="23"/>
-      <c r="AB6" s="23" t="s">
+      <c r="AA6" s="24"/>
+      <c r="AB6" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="AC6" s="23"/>
-      <c r="AD6" s="23"/>
-      <c r="AE6" s="23"/>
-      <c r="AF6" s="23"/>
-      <c r="AG6" s="23"/>
-      <c r="AH6" s="23"/>
+      <c r="AC6" s="24"/>
+      <c r="AD6" s="24"/>
+      <c r="AE6" s="24"/>
+      <c r="AF6" s="24"/>
+      <c r="AG6" s="24"/>
+      <c r="AH6" s="24"/>
     </row>
     <row r="7" spans="1:38" s="3" customFormat="1" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23" t="s">
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="24"/>
       <c r="F7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G7" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23" t="s">
+      <c r="H7" s="24"/>
+      <c r="I7" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23" t="s">
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
       <c r="O7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="P7" s="23" t="s">
+      <c r="P7" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="Q7" s="23" t="s">
+      <c r="Q7" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="R7" s="23" t="s">
+      <c r="R7" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="S7" s="23" t="s">
+      <c r="S7" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="T7" s="23" t="s">
+      <c r="T7" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="U7" s="23" t="s">
+      <c r="U7" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="V7" s="23"/>
-      <c r="W7" s="23"/>
-      <c r="X7" s="23" t="s">
+      <c r="V7" s="24"/>
+      <c r="W7" s="24"/>
+      <c r="X7" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="23" t="s">
+      <c r="Y7" s="24"/>
+      <c r="Z7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="AA7" s="23" t="s">
+      <c r="AA7" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="AB7" s="23" t="s">
+      <c r="AB7" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="AC7" s="23"/>
-      <c r="AD7" s="23"/>
-      <c r="AE7" s="23" t="s">
+      <c r="AC7" s="24"/>
+      <c r="AD7" s="24"/>
+      <c r="AE7" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="AF7" s="23"/>
-      <c r="AG7" s="23"/>
-      <c r="AH7" s="23"/>
+      <c r="AF7" s="24"/>
+      <c r="AG7" s="24"/>
+      <c r="AH7" s="24"/>
     </row>
     <row r="8" spans="1:38" s="3" customFormat="1" ht="49.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
       <c r="D8" s="4" t="s">
         <v>27</v>
       </c>
@@ -1740,11 +1573,11 @@
       <c r="O8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
       <c r="U8" s="4" t="s">
         <v>34</v>
       </c>
@@ -1760,8 +1593,8 @@
       <c r="Y8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="Z8" s="23"/>
-      <c r="AA8" s="23"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="24"/>
       <c r="AB8" s="4" t="s">
         <v>32</v>
       </c>
@@ -1785,8 +1618,8 @@
       </c>
     </row>
     <row r="9" spans="1:38" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="23"/>
-      <c r="B9" s="23"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
       <c r="C9" s="6" t="s">
         <v>39</v>
       </c>
@@ -1885,7 +1718,7 @@
       </c>
     </row>
     <row r="10" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="29" t="s">
         <v>50</v>
       </c>
       <c r="B10" s="7">
@@ -2025,7 +1858,7 @@
       <c r="AL10" s="8"/>
     </row>
     <row r="11" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="29"/>
+      <c r="A11" s="30"/>
       <c r="B11" s="7">
         <v>0.375</v>
       </c>
@@ -2163,7 +1996,7 @@
       <c r="AL11" s="8"/>
     </row>
     <row r="12" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
+      <c r="A12" s="30"/>
       <c r="B12" s="7">
         <v>0.41666666666666669</v>
       </c>
@@ -2301,7 +2134,7 @@
       <c r="AL12" s="8"/>
     </row>
     <row r="13" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="29"/>
+      <c r="A13" s="30"/>
       <c r="B13" s="7">
         <v>0.45833333333333331</v>
       </c>
@@ -2439,7 +2272,7 @@
       <c r="AL13" s="8"/>
     </row>
     <row r="14" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="29"/>
+      <c r="A14" s="30"/>
       <c r="B14" s="7">
         <v>0.5</v>
       </c>
@@ -2577,7 +2410,7 @@
       <c r="AL14" s="8"/>
     </row>
     <row r="15" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="29"/>
+      <c r="A15" s="30"/>
       <c r="B15" s="7">
         <v>0.54166666666666663</v>
       </c>
@@ -2715,7 +2548,7 @@
       <c r="AL15" s="8"/>
     </row>
     <row r="16" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="29"/>
+      <c r="A16" s="30"/>
       <c r="B16" s="7">
         <v>0.58333333333333337</v>
       </c>
@@ -2853,7 +2686,7 @@
       <c r="AL16" s="8"/>
     </row>
     <row r="17" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="29"/>
+      <c r="A17" s="30"/>
       <c r="B17" s="7">
         <v>0.625</v>
       </c>
@@ -2991,7 +2824,7 @@
       <c r="AL17" s="8"/>
     </row>
     <row r="18" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="29"/>
+      <c r="A18" s="30"/>
       <c r="B18" s="7">
         <v>0.66666666666666663</v>
       </c>
@@ -3129,7 +2962,7 @@
       <c r="AL18" s="8"/>
     </row>
     <row r="19" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="29"/>
+      <c r="A19" s="30"/>
       <c r="B19" s="7">
         <v>0.70833333333333337</v>
       </c>
@@ -3267,7 +3100,7 @@
       <c r="AL19" s="8"/>
     </row>
     <row r="20" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="29"/>
+      <c r="A20" s="30"/>
       <c r="B20" s="7">
         <v>0.75</v>
       </c>
@@ -3405,7 +3238,7 @@
       <c r="AL20" s="8"/>
     </row>
     <row r="21" spans="1:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
+      <c r="A21" s="31"/>
       <c r="B21" s="7">
         <v>0.79166666666666663</v>
       </c>
@@ -3543,7 +3376,7 @@
       <c r="AL21" s="8"/>
     </row>
     <row r="22" spans="1:38" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="24" t="s">
         <v>50</v>
       </c>
       <c r="B22" s="7">
@@ -3683,7 +3516,7 @@
       <c r="AL22" s="8"/>
     </row>
     <row r="23" spans="1:38" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="23"/>
+      <c r="A23" s="24"/>
       <c r="B23" s="7">
         <v>0.875</v>
       </c>
@@ -3821,7 +3654,7 @@
       <c r="AL23" s="8"/>
     </row>
     <row r="24" spans="1:38" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="23"/>
+      <c r="A24" s="24"/>
       <c r="B24" s="7">
         <v>0.91666666666666696</v>
       </c>
@@ -3959,7 +3792,7 @@
       <c r="AL24" s="8"/>
     </row>
     <row r="25" spans="1:38" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="23"/>
+      <c r="A25" s="24"/>
       <c r="B25" s="7">
         <v>0.95833333333333304</v>
       </c>
@@ -4097,7 +3930,7 @@
       <c r="AL25" s="8"/>
     </row>
     <row r="26" spans="1:38" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="23"/>
+      <c r="A26" s="24"/>
       <c r="B26" s="7">
         <v>1</v>
       </c>
@@ -4235,7 +4068,7 @@
       <c r="AL26" s="8"/>
     </row>
     <row r="27" spans="1:38" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="23"/>
+      <c r="A27" s="24"/>
       <c r="B27" s="7">
         <v>1.0416666666666701</v>
       </c>
@@ -4373,7 +4206,7 @@
       <c r="AL27" s="8"/>
     </row>
     <row r="28" spans="1:38" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="23"/>
+      <c r="A28" s="24"/>
       <c r="B28" s="7">
         <v>1.0833333333333299</v>
       </c>
@@ -4511,7 +4344,7 @@
       <c r="AL28" s="8"/>
     </row>
     <row r="29" spans="1:38" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="23"/>
+      <c r="A29" s="24"/>
       <c r="B29" s="7">
         <v>1.125</v>
       </c>
@@ -4649,7 +4482,7 @@
       <c r="AL29" s="8"/>
     </row>
     <row r="30" spans="1:38" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="23"/>
+      <c r="A30" s="24"/>
       <c r="B30" s="7">
         <v>1.1666666666666701</v>
       </c>
@@ -4787,7 +4620,7 @@
       <c r="AL30" s="8"/>
     </row>
     <row r="31" spans="1:38" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="23"/>
+      <c r="A31" s="24"/>
       <c r="B31" s="7">
         <v>1.2083333333333299</v>
       </c>
@@ -4925,7 +4758,7 @@
       <c r="AL31" s="8"/>
     </row>
     <row r="32" spans="1:38" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="23"/>
+      <c r="A32" s="24"/>
       <c r="B32" s="7">
         <v>1.25</v>
       </c>
@@ -5063,7 +4896,7 @@
       <c r="AL32" s="8"/>
     </row>
     <row r="33" spans="1:38" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="23"/>
+      <c r="A33" s="24"/>
       <c r="B33" s="7">
         <v>1.2916666666666601</v>
       </c>
@@ -5201,92 +5034,92 @@
       <c r="AL33" s="8"/>
     </row>
     <row r="34" spans="1:38" s="5" customFormat="1" ht="44.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="23" t="s">
+      <c r="A34" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23" t="s">
+      <c r="B34" s="24"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="H34" s="23"/>
-      <c r="I34" s="31" t="s">
+      <c r="H34" s="24"/>
+      <c r="I34" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
-      <c r="O34" s="31"/>
-      <c r="P34" s="23" t="s">
+      <c r="J34" s="32"/>
+      <c r="K34" s="32"/>
+      <c r="L34" s="32"/>
+      <c r="M34" s="32"/>
+      <c r="N34" s="32"/>
+      <c r="O34" s="32"/>
+      <c r="P34" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="Q34" s="23"/>
-      <c r="R34" s="23"/>
-      <c r="S34" s="23"/>
-      <c r="T34" s="23"/>
-      <c r="U34" s="23"/>
-      <c r="V34" s="23"/>
-      <c r="W34" s="23"/>
-      <c r="X34" s="23"/>
-      <c r="Y34" s="23"/>
-      <c r="Z34" s="23"/>
-      <c r="AA34" s="31" t="s">
+      <c r="Q34" s="24"/>
+      <c r="R34" s="24"/>
+      <c r="S34" s="24"/>
+      <c r="T34" s="24"/>
+      <c r="U34" s="24"/>
+      <c r="V34" s="24"/>
+      <c r="W34" s="24"/>
+      <c r="X34" s="24"/>
+      <c r="Y34" s="24"/>
+      <c r="Z34" s="24"/>
+      <c r="AA34" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="AB34" s="31"/>
-      <c r="AC34" s="31"/>
-      <c r="AD34" s="31"/>
-      <c r="AE34" s="31"/>
-      <c r="AF34" s="31"/>
-      <c r="AG34" s="31"/>
-      <c r="AH34" s="31"/>
+      <c r="AB34" s="32"/>
+      <c r="AC34" s="32"/>
+      <c r="AD34" s="32"/>
+      <c r="AE34" s="32"/>
+      <c r="AF34" s="32"/>
+      <c r="AG34" s="32"/>
+      <c r="AH34" s="32"/>
     </row>
     <row r="35" spans="1:38" s="5" customFormat="1" ht="44.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="23"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="31" t="s">
+      <c r="A35" s="24"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
-      <c r="O35" s="31"/>
-      <c r="P35" s="23" t="s">
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
+      <c r="L35" s="32"/>
+      <c r="M35" s="32"/>
+      <c r="N35" s="32"/>
+      <c r="O35" s="32"/>
+      <c r="P35" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="Q35" s="23"/>
-      <c r="R35" s="23"/>
-      <c r="S35" s="23"/>
-      <c r="T35" s="23"/>
-      <c r="U35" s="23"/>
-      <c r="V35" s="23"/>
-      <c r="W35" s="23"/>
-      <c r="X35" s="23"/>
-      <c r="Y35" s="23"/>
-      <c r="Z35" s="23"/>
-      <c r="AA35" s="31" t="s">
+      <c r="Q35" s="24"/>
+      <c r="R35" s="24"/>
+      <c r="S35" s="24"/>
+      <c r="T35" s="24"/>
+      <c r="U35" s="24"/>
+      <c r="V35" s="24"/>
+      <c r="W35" s="24"/>
+      <c r="X35" s="24"/>
+      <c r="Y35" s="24"/>
+      <c r="Z35" s="24"/>
+      <c r="AA35" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="AB35" s="31"/>
-      <c r="AC35" s="31"/>
-      <c r="AD35" s="31"/>
-      <c r="AE35" s="31"/>
-      <c r="AF35" s="31"/>
-      <c r="AG35" s="31"/>
-      <c r="AH35" s="31"/>
+      <c r="AB35" s="32"/>
+      <c r="AC35" s="32"/>
+      <c r="AD35" s="32"/>
+      <c r="AE35" s="32"/>
+      <c r="AF35" s="32"/>
+      <c r="AG35" s="32"/>
+      <c r="AH35" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="40">
@@ -5336,7 +5169,6 @@
   <headerFooter>
     <oddFooter>&amp;C&amp;P/&amp;N</oddFooter>
   </headerFooter>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5353,9 +5185,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="39"/>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
+      <c r="A1" s="38"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
       <c r="D1" s="12"/>
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
@@ -5369,56 +5201,56 @@
       <c r="N1" s="12"/>
       <c r="O1" s="12"/>
       <c r="P1" s="12"/>
-      <c r="Q1" s="40" t="s">
+      <c r="Q1" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
     </row>
     <row r="2" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="41" t="s">
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="42" t="s">
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="41"/>
+      <c r="T2" s="41"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="39"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
+      <c r="A3" s="38"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
       <c r="Q3" s="12"/>
       <c r="R3" s="12"/>
       <c r="S3" s="12"/>
@@ -5449,11 +5281,11 @@
       <c r="T4" s="14"/>
     </row>
     <row r="5" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="45"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="44"/>
       <c r="D5" s="15" t="s">
         <v>64</v>
       </c>
@@ -5531,14 +5363,14 @@
       </c>
     </row>
     <row r="6" spans="1:28" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="46" t="s">
+      <c r="C6" s="36"/>
+      <c r="D6" s="22" t="s">
         <v>67</v>
       </c>
       <c r="E6" s="11">
@@ -5569,14 +5401,14 @@
       <c r="AB6" s="11"/>
     </row>
     <row r="7" spans="1:28" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="36"/>
-      <c r="B7" s="32" t="s">
+      <c r="A7" s="37"/>
+      <c r="B7" s="33" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="22" t="s">
         <v>68</v>
       </c>
       <c r="E7" s="11"/>
@@ -5605,12 +5437,12 @@
       <c r="AB7" s="11"/>
     </row>
     <row r="8" spans="1:28" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="36"/>
-      <c r="B8" s="33"/>
+      <c r="A8" s="37"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="22" t="s">
         <v>69</v>
       </c>
       <c r="E8" s="11"/>
@@ -5639,14 +5471,14 @@
       <c r="AB8" s="11"/>
     </row>
     <row r="9" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="36"/>
+      <c r="A9" s="37"/>
       <c r="B9" s="18" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="46" t="s">
+      <c r="D9" s="22" t="s">
         <v>70</v>
       </c>
       <c r="E9" s="6"/>
@@ -5675,14 +5507,14 @@
       <c r="AB9" s="6"/>
     </row>
     <row r="10" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="36"/>
-      <c r="B10" s="32" t="s">
+      <c r="A10" s="37"/>
+      <c r="B10" s="33" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D10" s="22" t="s">
         <v>71</v>
       </c>
       <c r="E10" s="6"/>
@@ -5711,12 +5543,12 @@
       <c r="AB10" s="6"/>
     </row>
     <row r="11" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="22" t="s">
         <v>72</v>
       </c>
       <c r="E11" s="6"/>
@@ -5745,16 +5577,16 @@
       <c r="AB11" s="6"/>
     </row>
     <row r="12" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="22" t="s">
         <v>73</v>
       </c>
       <c r="E12" s="6"/>
@@ -5783,12 +5615,12 @@
       <c r="AB12" s="6"/>
     </row>
     <row r="13" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="36"/>
-      <c r="B13" s="36"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
       <c r="C13" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="46" t="s">
+      <c r="D13" s="22" t="s">
         <v>74</v>
       </c>
       <c r="E13" s="6"/>
@@ -5817,12 +5649,12 @@
       <c r="AB13" s="6"/>
     </row>
     <row r="14" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="36"/>
-      <c r="B14" s="33"/>
+      <c r="A14" s="37"/>
+      <c r="B14" s="34"/>
       <c r="C14" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="22" t="s">
         <v>75</v>
       </c>
       <c r="E14" s="6"/>
@@ -5851,14 +5683,14 @@
       <c r="AB14" s="6"/>
     </row>
     <row r="15" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="36"/>
-      <c r="B15" s="32" t="s">
+      <c r="A15" s="37"/>
+      <c r="B15" s="33" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D15" s="22" t="s">
         <v>76</v>
       </c>
       <c r="E15" s="6"/>
@@ -5887,12 +5719,12 @@
       <c r="AB15" s="6"/>
     </row>
     <row r="16" spans="1:28" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="36"/>
-      <c r="B16" s="36"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="37"/>
       <c r="C16" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="46" t="s">
+      <c r="D16" s="22" t="s">
         <v>77</v>
       </c>
       <c r="E16" s="21">
@@ -5923,12 +5755,12 @@
       <c r="AB16" s="21"/>
     </row>
     <row r="17" spans="1:28" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="36"/>
-      <c r="B17" s="33"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="34"/>
       <c r="C17" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="46" t="s">
+      <c r="D17" s="22" t="s">
         <v>78</v>
       </c>
       <c r="E17" s="21"/>
@@ -5957,14 +5789,14 @@
       <c r="AB17" s="21"/>
     </row>
     <row r="18" spans="1:28" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="33"/>
+      <c r="A18" s="34"/>
       <c r="B18" s="19" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="46" t="s">
+      <c r="D18" s="22" t="s">
         <v>79</v>
       </c>
       <c r="E18" s="21"/>
@@ -5993,14 +5825,14 @@
       <c r="AB18" s="21"/>
     </row>
     <row r="19" spans="1:28" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="46" t="s">
+      <c r="C19" s="36"/>
+      <c r="D19" s="22" t="s">
         <v>80</v>
       </c>
       <c r="E19" s="21"/>
@@ -6029,12 +5861,12 @@
       <c r="AB19" s="21"/>
     </row>
     <row r="20" spans="1:28" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="36"/>
-      <c r="B20" s="34" t="s">
+      <c r="A20" s="37"/>
+      <c r="B20" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="46" t="s">
+      <c r="C20" s="36"/>
+      <c r="D20" s="22" t="s">
         <v>81</v>
       </c>
       <c r="E20" s="21"/>
@@ -6063,12 +5895,12 @@
       <c r="AB20" s="21"/>
     </row>
     <row r="21" spans="1:28" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="36"/>
-      <c r="B21" s="37" t="s">
+      <c r="A21" s="37"/>
+      <c r="B21" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="38"/>
-      <c r="D21" s="46" t="s">
+      <c r="C21" s="46"/>
+      <c r="D21" s="22" t="s">
         <v>82</v>
       </c>
       <c r="E21" s="21"/>
@@ -6097,12 +5929,12 @@
       <c r="AB21" s="21"/>
     </row>
     <row r="22" spans="1:28" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="36"/>
-      <c r="B22" s="34" t="s">
+      <c r="A22" s="37"/>
+      <c r="B22" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="46" t="s">
+      <c r="C22" s="36"/>
+      <c r="D22" s="22" t="s">
         <v>83</v>
       </c>
       <c r="E22" s="21"/>
@@ -6131,12 +5963,12 @@
       <c r="AB22" s="21"/>
     </row>
     <row r="23" spans="1:28" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="33"/>
-      <c r="B23" s="34" t="s">
+      <c r="A23" s="34"/>
+      <c r="B23" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="35"/>
-      <c r="D23" s="46" t="s">
+      <c r="C23" s="36"/>
+      <c r="D23" s="22" t="s">
         <v>84</v>
       </c>
       <c r="E23" s="21"/>
@@ -6165,16 +5997,16 @@
       <c r="AB23" s="21"/>
     </row>
     <row r="24" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="32" t="s">
+      <c r="A24" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="32" t="s">
+      <c r="B24" s="33" t="s">
         <v>13</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D24" s="46" t="s">
+      <c r="D24" s="22" t="s">
         <v>85</v>
       </c>
       <c r="E24" s="6"/>
@@ -6203,12 +6035,12 @@
       <c r="AB24" s="6"/>
     </row>
     <row r="25" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A25" s="36"/>
-      <c r="B25" s="36"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="37"/>
       <c r="C25" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D25" s="46" t="s">
+      <c r="D25" s="22" t="s">
         <v>86</v>
       </c>
       <c r="E25" s="6"/>
@@ -6237,12 +6069,12 @@
       <c r="AB25" s="6"/>
     </row>
     <row r="26" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="36"/>
-      <c r="B26" s="33"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="34"/>
       <c r="C26" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="46" t="s">
+      <c r="D26" s="22" t="s">
         <v>87</v>
       </c>
       <c r="E26" s="6"/>
@@ -6271,14 +6103,14 @@
       <c r="AB26" s="6"/>
     </row>
     <row r="27" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="36"/>
-      <c r="B27" s="32" t="s">
+      <c r="A27" s="37"/>
+      <c r="B27" s="33" t="s">
         <v>14</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="46" t="s">
+      <c r="D27" s="22" t="s">
         <v>88</v>
       </c>
       <c r="E27" s="6"/>
@@ -6307,12 +6139,12 @@
       <c r="AB27" s="6"/>
     </row>
     <row r="28" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="33"/>
-      <c r="B28" s="33"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="34"/>
       <c r="C28" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="46" t="s">
+      <c r="D28" s="22" t="s">
         <v>89</v>
       </c>
       <c r="E28" s="6"/>
@@ -6341,14 +6173,14 @@
       <c r="AB28" s="6"/>
     </row>
     <row r="29" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="32" t="s">
+      <c r="A29" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="C29" s="35"/>
-      <c r="D29" s="46" t="s">
+      <c r="C29" s="36"/>
+      <c r="D29" s="22" t="s">
         <v>90</v>
       </c>
       <c r="E29" s="6"/>
@@ -6377,12 +6209,12 @@
       <c r="AB29" s="6"/>
     </row>
     <row r="30" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="33"/>
-      <c r="B30" s="34" t="s">
+      <c r="A30" s="34"/>
+      <c r="B30" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="C30" s="35"/>
-      <c r="D30" s="46" t="s">
+      <c r="C30" s="36"/>
+      <c r="D30" s="22" t="s">
         <v>91</v>
       </c>
       <c r="E30" s="6"/>
@@ -6411,16 +6243,16 @@
       <c r="AB30" s="6"/>
     </row>
     <row r="31" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A31" s="32" t="s">
+      <c r="A31" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="33" t="s">
         <v>25</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="D31" s="46" t="s">
+      <c r="D31" s="22" t="s">
         <v>92</v>
       </c>
       <c r="E31" s="6"/>
@@ -6449,12 +6281,12 @@
       <c r="AB31" s="6"/>
     </row>
     <row r="32" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="36"/>
-      <c r="B32" s="36"/>
+      <c r="A32" s="37"/>
+      <c r="B32" s="37"/>
       <c r="C32" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D32" s="46" t="s">
+      <c r="D32" s="22" t="s">
         <v>93</v>
       </c>
       <c r="E32" s="6"/>
@@ -6483,12 +6315,12 @@
       <c r="AB32" s="6"/>
     </row>
     <row r="33" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="36"/>
-      <c r="B33" s="33"/>
+      <c r="A33" s="37"/>
+      <c r="B33" s="34"/>
       <c r="C33" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="46" t="s">
+      <c r="D33" s="22" t="s">
         <v>94</v>
       </c>
       <c r="E33" s="6"/>
@@ -6517,14 +6349,14 @@
       <c r="AB33" s="6"/>
     </row>
     <row r="34" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A34" s="36"/>
-      <c r="B34" s="32" t="s">
+      <c r="A34" s="37"/>
+      <c r="B34" s="33" t="s">
         <v>26</v>
       </c>
       <c r="C34" s="18">
         <v>1</v>
       </c>
-      <c r="D34" s="46" t="s">
+      <c r="D34" s="22" t="s">
         <v>95</v>
       </c>
       <c r="E34" s="6">
@@ -6555,12 +6387,12 @@
       <c r="AB34" s="6"/>
     </row>
     <row r="35" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="36"/>
-      <c r="B35" s="36"/>
+      <c r="A35" s="37"/>
+      <c r="B35" s="37"/>
       <c r="C35" s="18">
         <v>2</v>
       </c>
-      <c r="D35" s="46" t="s">
+      <c r="D35" s="22" t="s">
         <v>96</v>
       </c>
       <c r="E35" s="6"/>
@@ -6589,12 +6421,12 @@
       <c r="AB35" s="6"/>
     </row>
     <row r="36" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="36"/>
-      <c r="B36" s="36"/>
+      <c r="A36" s="37"/>
+      <c r="B36" s="37"/>
       <c r="C36" s="18">
         <v>3</v>
       </c>
-      <c r="D36" s="46" t="s">
+      <c r="D36" s="22" t="s">
         <v>97</v>
       </c>
       <c r="E36" s="6"/>
@@ -6623,12 +6455,12 @@
       <c r="AB36" s="6"/>
     </row>
     <row r="37" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="33"/>
-      <c r="B37" s="33"/>
+      <c r="A37" s="34"/>
+      <c r="B37" s="34"/>
       <c r="C37" s="18">
         <v>4</v>
       </c>
-      <c r="D37" s="46" t="s">
+      <c r="D37" s="22" t="s">
         <v>98</v>
       </c>
       <c r="E37" s="6"/>
@@ -6658,12 +6490,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A12:A18"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="A19:A23"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
     <mergeCell ref="A24:A28"/>
     <mergeCell ref="B24:B26"/>
     <mergeCell ref="B27:B28"/>
@@ -6672,13 +6498,19 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="A12:A18"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="A19:A23"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="A1:C3"/>
     <mergeCell ref="Q1:T1"/>
     <mergeCell ref="D2:P3"/>
     <mergeCell ref="Q2:T2"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
